--- a/sharedata/excel/D-单位状态表(UnitStatusData).xlsx
+++ b/sharedata/excel/D-单位状态表(UnitStatusData).xlsx
@@ -5,14 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255" tabRatio="688"/>
   </bookViews>
   <sheets>
-    <sheet name="稀有度表(UnitRateData)" sheetId="3" r:id="rId1"/>
+    <sheet name="单位状态表(UnitStateData)" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -233,7 +233,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
@@ -459,11 +459,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -964,7 +959,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyFill="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="1" applyFill="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyFill="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellStyleXfs>
